--- a/extension_forms/026_extension_application_fee_payment_form--extension_forms.xlsx
+++ b/extension_forms/026_extension_application_fee_payment_form--extension_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'bank_transfer'}</t>
+          <t>bank transfer</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'credit_card'}</t>
+          <t>credit card</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
     </row>
